--- a/Files/DOCUMENTO_DE_PROYECTO_INICIO_RutasTuristicas.xlsx
+++ b/Files/DOCUMENTO_DE_PROYECTO_INICIO_RutasTuristicas.xlsx
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Reporta a: Jefe del Proyecto – Fabián Guerra</t>
+          <t>Reporta a: Jefe del Proyecto – Marcelo Tapia</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>Reporta a: Jefe del Proyecto – Fabián Guerra</t>
+          <t>Reporta a: Jefe del Proyecto – Marcelo Tapia</t>
         </is>
       </c>
       <c r="C30" s="34" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>Reporta a: Jefe del Proyecto – Fabián Guerra</t>
+          <t>Reporta a: Jefe del Proyecto – Marcelo Tapia</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Nombre: Fabián Guerra</t>
+          <t>Nombre: Marcelo Tapia</t>
         </is>
       </c>
       <c r="C50" s="33" t="inlineStr">
